--- a/正态分布随机误差生成器.xlsx
+++ b/正态分布随机误差生成器.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Repos\fuck-UPE\大物实验\数据处理-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Repos\fuck-UPE\大物实验\数据处理-保护branch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78BA9C46-6C44-4B1A-AEC1-1DC68E817EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB10323-3CAC-415A-AB76-2A56A095BBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -696,11 +696,11 @@
       </c>
       <c r="B19" s="11">
         <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
-        <v>4.8899999999999997</v>
+        <v>4.9009999999999998</v>
       </c>
       <c r="C19" s="11">
         <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
-        <v>4.9039999999999999</v>
+        <v>4.9009999999999998</v>
       </c>
       <c r="D19" s="11">
         <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
@@ -708,51 +708,51 @@
       </c>
       <c r="E19" s="11">
         <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
-        <v>4.8949999999999996</v>
+        <v>4.8890000000000002</v>
       </c>
       <c r="F19" s="11">
         <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
+        <v>4.9089999999999998</v>
+      </c>
+      <c r="G19" s="11">
+        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
+        <v>4.891</v>
+      </c>
+      <c r="H19" s="11">
+        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
+        <v>4.8940000000000001</v>
+      </c>
+      <c r="I19" s="11">
+        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J19" s="11">
+        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K19" s="11">
+        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
+        <v>4.9089999999999998</v>
+      </c>
+      <c r="L19" s="11">
+        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
+        <v>4.9009999999999998</v>
+      </c>
+      <c r="M19" s="11">
+        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
+        <v>4.9109999999999996</v>
+      </c>
+      <c r="N19" s="11">
+        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
         <v>4.9119999999999999</v>
       </c>
-      <c r="G19" s="11">
-        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
-        <v>4.8860000000000001</v>
-      </c>
-      <c r="H19" s="11">
-        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
-        <v>4.8959999999999999</v>
-      </c>
-      <c r="I19" s="11">
-        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
-        <v>4.8890000000000002</v>
-      </c>
-      <c r="J19" s="11">
-        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
-        <v>4.8959999999999999</v>
-      </c>
-      <c r="K19" s="11">
-        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
-        <v>4.899</v>
-      </c>
-      <c r="L19" s="11">
-        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
-        <v>4.899</v>
-      </c>
-      <c r="M19" s="11">
-        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
-        <v>4.899</v>
-      </c>
-      <c r="N19" s="11">
-        <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
-        <v>4.8890000000000002</v>
-      </c>
       <c r="O19" s="11">
         <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
-        <v>4.8979999999999997</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="P19" s="11">
         <f ca="1">ROUND(_xlfn.NORM.INV(RAND(),B16, D16),E16)</f>
-        <v>4.891</v>
+        <v>4.9050000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
@@ -761,11 +761,11 @@
       </c>
       <c r="B20" s="11">
         <f ca="1">B18+B19</f>
-        <v>31.311</v>
+        <v>31.321999999999999</v>
       </c>
       <c r="C20" s="11">
         <f t="shared" ref="C20:P20" ca="1" si="0">C18+C19</f>
-        <v>30.826000000000001</v>
+        <v>30.823</v>
       </c>
       <c r="D20" s="11">
         <f t="shared" ca="1" si="0"/>
@@ -773,51 +773,51 @@
       </c>
       <c r="E20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>30.373000000000001</v>
+        <v>30.367000000000001</v>
       </c>
       <c r="F20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>29.582000000000001</v>
+        <v>29.579000000000001</v>
       </c>
       <c r="G20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>29.230999999999998</v>
+        <v>29.235999999999997</v>
       </c>
       <c r="H20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>28.926000000000002</v>
+        <v>28.923999999999999</v>
       </c>
       <c r="I20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>4.8890000000000002</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="J20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>4.8959999999999999</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="K20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>4.899</v>
+        <v>4.9089999999999998</v>
       </c>
       <c r="L20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>4.899</v>
+        <v>4.9009999999999998</v>
       </c>
       <c r="M20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>4.899</v>
+        <v>4.9109999999999996</v>
       </c>
       <c r="N20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>4.8890000000000002</v>
+        <v>4.9119999999999999</v>
       </c>
       <c r="O20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>4.8979999999999997</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="P20" s="11">
         <f t="shared" ca="1" si="0"/>
-        <v>4.891</v>
+        <v>4.9050000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -844,6 +844,7 @@
       <c r="A30" s="10"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
